--- a/data/trans_orig/P16A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>42772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55447</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253226</t>
+          <t>252641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267000</t>
+          <t>267072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219081</t>
+          <t>218066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239510</t>
+          <t>239594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>478401</t>
+          <t>477649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>503465</t>
+          <t>502761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50888</t>
+          <t>49890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81064</t>
+          <t>80043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67010</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102606</t>
+          <t>99728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465604</t>
+          <t>465249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>482163</t>
+          <t>481981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422885</t>
+          <t>423906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>453061</t>
+          <t>454059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>894418</t>
+          <t>897296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930014</t>
+          <t>929588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>27513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>38882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301260</t>
+          <t>301267</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314544</t>
+          <t>314183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307758</t>
+          <t>307899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324373</t>
+          <t>324356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613738</t>
+          <t>615376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635263</t>
+          <t>635510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43352</t>
+          <t>45018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32506</t>
+          <t>31748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56541</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339289</t>
+          <t>341373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353167</t>
+          <t>353835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328104</t>
+          <t>326438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348710</t>
+          <t>348154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>673586</t>
+          <t>674127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>697621</t>
+          <t>698379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>45132</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60249</t>
+          <t>61197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181095</t>
+          <t>181806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195311</t>
+          <t>195291</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162695</t>
+          <t>162536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183851</t>
+          <t>184376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>350727</t>
+          <t>349779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375903</t>
+          <t>375299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258086</t>
+          <t>259019</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268003</t>
+          <t>268811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249166</t>
+          <t>249062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266165</t>
+          <t>266307</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513236</t>
+          <t>513551</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532570</t>
+          <t>533069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>20170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42529</t>
+          <t>40657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59606</t>
+          <t>60878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91026</t>
+          <t>92381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87690</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125359</t>
+          <t>126190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>572498</t>
+          <t>574370</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>595511</t>
+          <t>594857</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>547193</t>
+          <t>545838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>578613</t>
+          <t>577341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1127887</t>
+          <t>1127056</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1165556</t>
+          <t>1167405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49937</t>
+          <t>48761</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80482</t>
+          <t>79469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85261</t>
+          <t>84933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123694</t>
+          <t>122439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142900</t>
+          <t>141071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192593</t>
+          <t>193243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>663313</t>
+          <t>664326</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>693858</t>
+          <t>695034</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>659817</t>
+          <t>661072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>698250</t>
+          <t>698578</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1334713</t>
+          <t>1334063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1384406</t>
+          <t>1386235</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>137978</t>
+          <t>137711</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188322</t>
+          <t>186644</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>339971</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>413853</t>
+          <t>408540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>495709</t>
+          <t>499543</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>588787</t>
+          <t>582131</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3088221</t>
+          <t>3089899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3138565</t>
+          <t>3138832</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2965344</t>
+          <t>2970657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3037902</t>
+          <t>3039226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6066954</t>
+          <t>6073610</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6160032</t>
+          <t>6156198</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18986</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40691</t>
+          <t>41999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40999</t>
+          <t>41240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69644</t>
+          <t>69168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,47 +4106,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>83064</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>68081</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>102496</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>14,27%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>24,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>83064</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>68423</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>103296</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254047</t>
+          <t>252739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275752</t>
+          <t>274415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>217601</t>
+          <t>218077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246246</t>
+          <t>246005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,47 +4219,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>85,64%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>498919</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>479487</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>513902</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>85,73%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>498919</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>478687</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>513560</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>85,73%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45511</t>
+          <t>45203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71151</t>
+          <t>71242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107753</t>
+          <t>107494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95984</t>
+          <t>97000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138512</t>
+          <t>140466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460016</t>
+          <t>460324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>487681</t>
+          <t>486191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416012</t>
+          <t>416271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452614</t>
+          <t>452523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890780</t>
+          <t>888826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933308</t>
+          <t>932292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17173</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>39303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33935</t>
+          <t>34005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58873</t>
+          <t>60105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56306</t>
+          <t>57114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89642</t>
+          <t>89416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284495</t>
+          <t>284743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306873</t>
+          <t>306275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282147</t>
+          <t>280915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307085</t>
+          <t>307015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575424</t>
+          <t>575650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>607952</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>27948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52891</t>
+          <t>53864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>83057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70450</t>
+          <t>69212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105288</t>
+          <t>105313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344024</t>
+          <t>346034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362364</t>
+          <t>363007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>306899</t>
+          <t>305894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>336060</t>
+          <t>335087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657645</t>
+          <t>657620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692483</t>
+          <t>693721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71564</t>
+          <t>71758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>84363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193787</t>
+          <t>192955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207208</t>
+          <t>207116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148027</t>
+          <t>147833</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174649</t>
+          <t>174705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347128</t>
+          <t>347846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377837</t>
+          <t>379649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31889</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31454</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>57550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49748</t>
+          <t>49776</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79575</t>
+          <t>80827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242092</t>
+          <t>242388</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261110</t>
+          <t>261150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224282</t>
+          <t>222481</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248577</t>
+          <t>247218</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474437</t>
+          <t>473185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504264</t>
+          <t>504236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60013</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65583</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>100695</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151306</t>
+          <t>153799</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602775</t>
+          <t>600648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>629554</t>
+          <t>628974</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>593291</t>
+          <t>593158</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>628270</t>
+          <t>627928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1205335</t>
+          <t>1202842</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1250008</t>
+          <t>1249605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34899</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98045</t>
+          <t>99000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>140011</t>
+          <t>141810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142972</t>
+          <t>141752</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>191586</t>
+          <t>192952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>716316</t>
+          <t>715329</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>744199</t>
+          <t>743859</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>683842</t>
+          <t>682043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>725808</t>
+          <t>724853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1411365</t>
+          <t>1409999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1459979</t>
+          <t>1461199</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198997</t>
+          <t>198349</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>261076</t>
+          <t>262165</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>513093</t>
+          <t>507726</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>597912</t>
+          <t>595880</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>728374</t>
+          <t>732170</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>840686</t>
+          <t>840872</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3165703</t>
+          <t>3164614</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3227782</t>
+          <t>3228430</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2960397</t>
+          <t>2962429</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3045216</t>
+          <t>3050583</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6144402</t>
+          <t>6144216</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6256714</t>
+          <t>6252918</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40570</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>67262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60095</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93596</t>
+          <t>93098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259580</t>
+          <t>260155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279272</t>
+          <t>279266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221142</t>
+          <t>221441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248133</t>
+          <t>249170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488868</t>
+          <t>489366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>522369</t>
+          <t>523148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40324</t>
+          <t>40522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94490</t>
+          <t>91712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86160</t>
+          <t>85801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>126764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462251</t>
+          <t>462053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>483094</t>
+          <t>483588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428594</t>
+          <t>431372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461798</t>
+          <t>464001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>898895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939499</t>
+          <t>939858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53589</t>
+          <t>53239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>40369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67598</t>
+          <t>68049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>298725</t>
+          <t>297561</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312466</t>
+          <t>312432</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282720</t>
+          <t>283070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306562</t>
+          <t>306611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>587276</t>
+          <t>586825</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614934</t>
+          <t>614505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48041</t>
+          <t>48588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77484</t>
+          <t>78621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>67592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103881</t>
+          <t>101648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>338022</t>
+          <t>337197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355516</t>
+          <t>356121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309799</t>
+          <t>308662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339242</t>
+          <t>338695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>653366</t>
+          <t>655599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>690572</t>
+          <t>689655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>43037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71273</t>
+          <t>70618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181264</t>
+          <t>181227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198169</t>
+          <t>198217</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169397</t>
+          <t>169490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192399</t>
+          <t>192419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>358535</t>
+          <t>359190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>385370</t>
+          <t>386771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>27076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35628</t>
+          <t>36559</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>61747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>51483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81841</t>
+          <t>82665</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236902</t>
+          <t>236047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252892</t>
+          <t>252507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212407</t>
+          <t>211368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237487</t>
+          <t>236556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454397</t>
+          <t>453573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484536</t>
+          <t>484755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>36199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63449</t>
+          <t>64245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76280</t>
+          <t>79159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116415</t>
+          <t>118235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123990</t>
+          <t>121602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171187</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>593109</t>
+          <t>592313</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621459</t>
+          <t>620359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>574879</t>
+          <t>573059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>615014</t>
+          <t>612135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1176665</t>
+          <t>1179815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1223862</t>
+          <t>1226250</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105501</t>
+          <t>107558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149433</t>
+          <t>151988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143099</t>
+          <t>144601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195555</t>
+          <t>198505</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>723465</t>
+          <t>722610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>748525</t>
+          <t>748150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>676734</t>
+          <t>674179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>720666</t>
+          <t>718609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1409195</t>
+          <t>1406245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1461651</t>
+          <t>1460149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>187163</t>
+          <t>184534</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>243107</t>
+          <t>240749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>495516</t>
+          <t>494082</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>583035</t>
+          <t>583729</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>696759</t>
+          <t>699388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>802928</t>
+          <t>800588</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3151243</t>
+          <t>3153601</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3207187</t>
+          <t>3209816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2961507</t>
+          <t>2960813</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3049026</t>
+          <t>3050460</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6135964</t>
+          <t>6138304</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6242133</t>
+          <t>6239504</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>13669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30128</t>
+          <t>30646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44752</t>
+          <t>45878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>69623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281315</t>
+          <t>280797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298052</t>
+          <t>297774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244883</t>
+          <t>243757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261045</t>
+          <t>260762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531261</t>
+          <t>531454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554586</t>
+          <t>554811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57227</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74630</t>
+          <t>75397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102030</t>
+          <t>102971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111738</t>
+          <t>111149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151973</t>
+          <t>150351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461163</t>
+          <t>461991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488813</t>
+          <t>488755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412939</t>
+          <t>411998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>440339</t>
+          <t>439572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>881386</t>
+          <t>883008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921621</t>
+          <t>922210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53329</t>
+          <t>54022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76879</t>
+          <t>76949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82678</t>
+          <t>81784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112698</t>
+          <t>113359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273651</t>
+          <t>273125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>292794</t>
+          <t>292409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272249</t>
+          <t>272179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295799</t>
+          <t>295106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552480</t>
+          <t>551819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582500</t>
+          <t>583394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29417</t>
+          <t>29534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>66937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57908</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>96786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271818</t>
+          <t>273070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294239</t>
+          <t>294124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>407976</t>
+          <t>408781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>446301</t>
+          <t>446184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>687754</t>
+          <t>691488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>730366</t>
+          <t>733256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17115</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>47409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58086</t>
+          <t>58300</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161627</t>
+          <t>161387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171127</t>
+          <t>171235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211684</t>
+          <t>211370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>240449</t>
+          <t>239159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379435</t>
+          <t>379221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405172</t>
+          <t>404133</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>49444</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>75853</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102392</t>
+          <t>102368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230138</t>
+          <t>230564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246457</t>
+          <t>246756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188487</t>
+          <t>188111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207533</t>
+          <t>207612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>424300</t>
+          <t>424324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>450018</t>
+          <t>450839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>40648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71854</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58991</t>
+          <t>57128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163737</t>
+          <t>165307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109878</t>
+          <t>109384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210708</t>
+          <t>213349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>552425</t>
+          <t>554454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583157</t>
+          <t>583631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>685528</t>
+          <t>683958</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>790274</t>
+          <t>792137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1260195</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1363666</t>
+          <t>1364160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25771</t>
+          <t>28858</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95191</t>
+          <t>95023</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128753</t>
+          <t>130597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>166664</t>
+          <t>168755</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136298</t>
+          <t>120395</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>260511</t>
+          <t>261356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>833529</t>
+          <t>833697</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>902949</t>
+          <t>899862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>551067</t>
+          <t>548976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>588978</t>
+          <t>587134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1385941</t>
+          <t>1385096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1510154</t>
+          <t>1526057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>225782</t>
+          <t>222400</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>324905</t>
+          <t>320799</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>478497</t>
+          <t>490632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>656282</t>
+          <t>660644</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>775592</t>
+          <t>760517</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>964118</t>
+          <t>961645</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3134912</t>
+          <t>3139018</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3234035</t>
+          <t>3237417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3055998</t>
+          <t>3051636</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3233783</t>
+          <t>3221648</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6207979</t>
+          <t>6210452</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6396505</t>
+          <t>6411580</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>19443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42772</t>
+          <t>41535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>31677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56199</t>
+          <t>58633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252641</t>
+          <t>253567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267072</t>
+          <t>267370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218066</t>
+          <t>219303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239594</t>
+          <t>240000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>477649</t>
+          <t>475215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>502761</t>
+          <t>502171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80043</t>
+          <t>79435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67436</t>
+          <t>66929</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99728</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465249</t>
+          <t>463934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481981</t>
+          <t>481528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423906</t>
+          <t>424514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454059</t>
+          <t>453513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>897296</t>
+          <t>895990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929588</t>
+          <t>930095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38882</t>
+          <t>39532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301267</t>
+          <t>300519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314183</t>
+          <t>314019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307899</t>
+          <t>307688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324356</t>
+          <t>324425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615376</t>
+          <t>614726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635510</t>
+          <t>635410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23302</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31748</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>57461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341373</t>
+          <t>340887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353835</t>
+          <t>353714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>326438</t>
+          <t>326225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348154</t>
+          <t>347853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674127</t>
+          <t>672666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>698379</t>
+          <t>698425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45132</t>
+          <t>47292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35677</t>
+          <t>35092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>61265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181806</t>
+          <t>181271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195291</t>
+          <t>195047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162536</t>
+          <t>160376</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184376</t>
+          <t>182486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>349779</t>
+          <t>349711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375299</t>
+          <t>375884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>28797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35404</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259019</t>
+          <t>258139</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268811</t>
+          <t>268836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249062</t>
+          <t>249347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>266307</t>
+          <t>266158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513551</t>
+          <t>513381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533069</t>
+          <t>532151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40657</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60878</t>
+          <t>59051</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92381</t>
+          <t>93378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85841</t>
+          <t>87962</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126190</t>
+          <t>125881</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>574370</t>
+          <t>574197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>594857</t>
+          <t>595115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>545838</t>
+          <t>544841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>577341</t>
+          <t>579168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1127056</t>
+          <t>1127365</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1167405</t>
+          <t>1165284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79469</t>
+          <t>78340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84933</t>
+          <t>84535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122439</t>
+          <t>124044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,47 +3184,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>165558</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>143314</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>192377</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>165558</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>141071</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>193243</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>665455</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>695034</t>
+          <t>695189</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>661072</t>
+          <t>659467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>698578</t>
+          <t>698976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,47 +3297,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1361748</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1334929</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1383992</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>89,16%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1361748</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1334063</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1386235</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>137711</t>
+          <t>135663</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187471</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>339971</t>
+          <t>342761</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>408540</t>
+          <t>412231</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>499543</t>
+          <t>495382</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>582131</t>
+          <t>586238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3089899</t>
+          <t>3089072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3138832</t>
+          <t>3140880</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2970657</t>
+          <t>2966966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3039226</t>
+          <t>3036436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6073610</t>
+          <t>6069503</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6156198</t>
+          <t>6160359</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41999</t>
+          <t>41495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41240</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69168</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68081</t>
+          <t>67380</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102496</t>
+          <t>102720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252739</t>
+          <t>253243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274415</t>
+          <t>275561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218077</t>
+          <t>217584</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246005</t>
+          <t>245209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479487</t>
+          <t>479263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>513902</t>
+          <t>514603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>72432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107494</t>
+          <t>107204</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97000</t>
+          <t>97220</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140466</t>
+          <t>142729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460324</t>
+          <t>461192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486191</t>
+          <t>487215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416271</t>
+          <t>416561</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452523</t>
+          <t>451333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888826</t>
+          <t>886563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932292</t>
+          <t>932072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34005</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60105</t>
+          <t>58996</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57114</t>
+          <t>57741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89416</t>
+          <t>90377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284743</t>
+          <t>283890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306275</t>
+          <t>306354</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280915</t>
+          <t>282024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307015</t>
+          <t>307812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575650</t>
+          <t>574689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>607952</t>
+          <t>607325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>51967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83057</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>68902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105313</t>
+          <t>104034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346034</t>
+          <t>344605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>363007</t>
+          <t>362289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305894</t>
+          <t>307624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>335087</t>
+          <t>336984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657620</t>
+          <t>658899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>693721</t>
+          <t>694031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44886</t>
+          <t>44749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71758</t>
+          <t>71665</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>52504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84363</t>
+          <t>83059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192955</t>
+          <t>192393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207116</t>
+          <t>206863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147833</t>
+          <t>147926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174705</t>
+          <t>174842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>347846</t>
+          <t>349150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379649</t>
+          <t>379705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>30682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57550</t>
+          <t>55890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49776</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80827</t>
+          <t>79159</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242388</t>
+          <t>243299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261150</t>
+          <t>261297</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222481</t>
+          <t>224141</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247218</t>
+          <t>248039</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>473185</t>
+          <t>474853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504236</t>
+          <t>503348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>33136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65925</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100695</t>
+          <t>101333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107036</t>
+          <t>104771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153799</t>
+          <t>147369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600648</t>
+          <t>600773</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>628974</t>
+          <t>629652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>593158</t>
+          <t>592520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>627928</t>
+          <t>627128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1202842</t>
+          <t>1209272</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1249605</t>
+          <t>1251870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>63769</t>
+          <t>60860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99000</t>
+          <t>98548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141810</t>
+          <t>138589</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141752</t>
+          <t>143109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192952</t>
+          <t>192886</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>715329</t>
+          <t>718238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>743859</t>
+          <t>745311</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>682043</t>
+          <t>685264</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>724853</t>
+          <t>725305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1409999</t>
+          <t>1410065</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1461199</t>
+          <t>1459842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198349</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>262165</t>
+          <t>259956</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>507726</t>
+          <t>515873</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>595880</t>
+          <t>602809</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>732170</t>
+          <t>727951</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>840872</t>
+          <t>834702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3164614</t>
+          <t>3166823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3228430</t>
+          <t>3231509</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2962429</t>
+          <t>2955500</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3050583</t>
+          <t>3042436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6144216</t>
+          <t>6150386</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6252918</t>
+          <t>6257137</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39533</t>
+          <t>40071</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67262</t>
+          <t>67407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>59188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93098</t>
+          <t>93736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260155</t>
+          <t>260405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279266</t>
+          <t>279272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221441</t>
+          <t>221296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249170</t>
+          <t>248632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>489366</t>
+          <t>488728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523148</t>
+          <t>523276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>40659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59083</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91712</t>
+          <t>94352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>85864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126764</t>
+          <t>126099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462053</t>
+          <t>461916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>483588</t>
+          <t>481959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431372</t>
+          <t>428732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464001</t>
+          <t>462940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>898895</t>
+          <t>899560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939858</t>
+          <t>939795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29698</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53239</t>
+          <t>52604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40369</t>
+          <t>39303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68049</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297561</t>
+          <t>297988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312432</t>
+          <t>312224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283070</t>
+          <t>283705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306611</t>
+          <t>306564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586825</t>
+          <t>587438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614505</t>
+          <t>615571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>31669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48588</t>
+          <t>48636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78621</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>68024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101648</t>
+          <t>104754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337197</t>
+          <t>338295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356121</t>
+          <t>356110</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>308662</t>
+          <t>308867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>338695</t>
+          <t>338647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655599</t>
+          <t>652493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>689655</t>
+          <t>689223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29994</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>26926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>48866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>43252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70618</t>
+          <t>71996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181227</t>
+          <t>181793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198217</t>
+          <t>199538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169490</t>
+          <t>169721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192419</t>
+          <t>191661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>359190</t>
+          <t>357812</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386771</t>
+          <t>386556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,94%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>10642</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36559</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>50322</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82665</t>
+          <t>80873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236047</t>
+          <t>235638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252507</t>
+          <t>252481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>211368</t>
+          <t>213684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236556</t>
+          <t>237949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>453573</t>
+          <t>455365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>484755</t>
+          <t>485916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36199</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64245</t>
+          <t>62970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79159</t>
+          <t>79884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118235</t>
+          <t>117989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121602</t>
+          <t>121519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168037</t>
+          <t>169823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>592313</t>
+          <t>593588</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>620359</t>
+          <t>621425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>573059</t>
+          <t>573305</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>612135</t>
+          <t>611410</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1179815</t>
+          <t>1178029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1226250</t>
+          <t>1226333</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>107558</t>
+          <t>107554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151988</t>
+          <t>154332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144601</t>
+          <t>144001</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198505</t>
+          <t>198418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>722610</t>
+          <t>723571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>748150</t>
+          <t>748548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>674179</t>
+          <t>671835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>718609</t>
+          <t>718613</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1406245</t>
+          <t>1406332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1460149</t>
+          <t>1460749</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>184534</t>
+          <t>186862</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>240749</t>
+          <t>243370</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>494082</t>
+          <t>500061</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>583729</t>
+          <t>586337</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>699388</t>
+          <t>696469</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>800588</t>
+          <t>802855</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3153601</t>
+          <t>3150980</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3209816</t>
+          <t>3207488</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2960813</t>
+          <t>2958205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3050460</t>
+          <t>3044481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6138304</t>
+          <t>6136037</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6239504</t>
+          <t>6242423</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>36320</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45878</t>
+          <t>46206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56984</t>
+          <t>58775</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46266</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69623</t>
+          <t>71416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>290779</t>
+          <t>297541</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280797</t>
+          <t>287137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297774</t>
+          <t>304448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>253315</t>
+          <t>278590</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>243757</t>
+          <t>269855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260762</t>
+          <t>286328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>544093</t>
+          <t>576131</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531454</t>
+          <t>563490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>554811</t>
+          <t>586514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>43751</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56399</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,67 +11075,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87965</t>
+          <t>91496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>78234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102971</t>
+          <t>106541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>135247</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>117489</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>157644</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>14,64%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>129838</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>111149</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>150351</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>476518</t>
+          <t>486896</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461991</t>
+          <t>470384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>488755</t>
+          <t>500862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,67 +11188,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>427004</t>
+          <t>454998</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411998</t>
+          <t>439953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439572</t>
+          <t>468260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>85,68%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>941894</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>919497</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>959652</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>85,36%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>903521</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>883008</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>922210</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>87,44%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64931</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54022</t>
+          <t>55480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76949</t>
+          <t>78229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>96187</t>
+          <t>98459</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>83676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113359</t>
+          <t>113410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>284794</t>
+          <t>283880</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273125</t>
+          <t>273143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>292409</t>
+          <t>292577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>284197</t>
+          <t>290034</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272179</t>
+          <t>278152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295106</t>
+          <t>300901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>568991</t>
+          <t>573916</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>551819</t>
+          <t>558965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>583394</t>
+          <t>588699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>44514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29534</t>
+          <t>43552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66937</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>84383</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>69232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96786</t>
+          <t>103333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>285016</t>
+          <t>343428</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273070</t>
+          <t>328631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>294124</t>
+          <t>353276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>425705</t>
+          <t>367295</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>408781</t>
+          <t>353459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>446184</t>
+          <t>378409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>710720</t>
+          <t>710724</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691488</t>
+          <t>691774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>733256</t>
+          <t>725875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>31625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47409</t>
+          <t>46095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>41528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58300</t>
+          <t>59911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>167157</t>
+          <t>193482</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161387</t>
+          <t>187814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171235</t>
+          <t>198203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>222629</t>
+          <t>190812</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211370</t>
+          <t>182823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239159</t>
+          <t>197293</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>389786</t>
+          <t>384293</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379221</t>
+          <t>374671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404133</t>
+          <t>393054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58116</t>
+          <t>59303</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49444</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68945</t>
+          <t>69556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>88514</t>
+          <t>89108</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75853</t>
+          <t>77884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102368</t>
+          <t>102402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239239</t>
+          <t>240902</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230564</t>
+          <t>232047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246756</t>
+          <t>247623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>198940</t>
+          <t>204447</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188111</t>
+          <t>194194</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207612</t>
+          <t>213565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>438178</t>
+          <t>445349</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>424324</t>
+          <t>432055</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>450839</t>
+          <t>456573</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>47350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69825</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>120446</t>
+          <t>140574</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>122395</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165307</t>
+          <t>160922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>202897</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109384</t>
+          <t>178407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213349</t>
+          <t>229186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>570535</t>
+          <t>657364</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>554454</t>
+          <t>639985</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>672337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>728819</t>
+          <t>631483</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683958</t>
+          <t>611135</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>792137</t>
+          <t>649662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1299354</t>
+          <t>1288847</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1260195</t>
+          <t>1262558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1364160</t>
+          <t>1313337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>74114</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28858</t>
+          <t>60693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95023</t>
+          <t>91007</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>148102</t>
+          <t>164511</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130597</t>
+          <t>144867</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168755</t>
+          <t>186134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>213643</t>
+          <t>238625</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120395</t>
+          <t>215795</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>261356</t>
+          <t>265504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>863179</t>
+          <t>723958</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>833697</t>
+          <t>707065</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>899862</t>
+          <t>737379</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>569629</t>
+          <t>666820</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>548976</t>
+          <t>645197</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>587134</t>
+          <t>686464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1432809</t>
+          <t>1390778</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1385096</t>
+          <t>1363899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1526057</t>
+          <t>1413608</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>282602</t>
+          <t>305311</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222400</t>
+          <t>270968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>320799</t>
+          <t>339187</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>602042</t>
+          <t>652472</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>490632</t>
+          <t>613414</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>660644</t>
+          <t>689803</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>884644</t>
+          <t>957783</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>760517</t>
+          <t>906063</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>961645</t>
+          <t>1009350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3177215</t>
+          <t>3227451</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3139018</t>
+          <t>3193575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3237417</t>
+          <t>3261794</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3110238</t>
+          <t>3084482</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3051636</t>
+          <t>3047151</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3221648</t>
+          <t>3123540</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6287453</t>
+          <t>6311933</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6210452</t>
+          <t>6260366</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6411580</t>
+          <t>6363653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
